--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="613">
   <si>
     <t>Property</t>
   </si>
@@ -633,7 +633,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -920,6 +920,14 @@
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP89803-8"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.category:second.id</t>
   </si>
   <si>
@@ -936,9 +944,6 @@
   </si>
   <si>
     <t>Observation.category:second.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.category:second.coding.version</t>
@@ -1073,6 +1078,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.code.coding.version</t>
@@ -4821,7 +4829,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -5586,7 +5594,7 @@
         <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>83</v>
@@ -5660,7 +5668,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>207</v>
@@ -5778,7 +5786,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>214</v>
@@ -5898,7 +5906,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>220</v>
@@ -6020,7 +6028,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>230</v>
@@ -6138,7 +6146,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>232</v>
@@ -6258,7 +6266,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>234</v>
@@ -6269,7 +6277,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>
@@ -6303,7 +6311,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -7715,7 +7723,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>
@@ -9195,7 +9203,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9272,10 +9280,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9392,10 +9400,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9435,7 +9443,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9512,10 +9520,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9558,7 +9566,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9632,10 +9640,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9754,10 +9762,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9876,10 +9884,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9902,19 +9910,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9963,7 +9971,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9978,19 +9986,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -9998,10 +10006,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10024,16 +10032,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10083,7 +10091,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10107,10 +10115,10 @@
         <v>331</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10118,14 +10126,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10144,19 +10152,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10205,7 +10213,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10220,19 +10228,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10240,14 +10248,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10266,19 +10274,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10327,7 +10335,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10342,19 +10350,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10362,10 +10370,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10388,16 +10396,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10447,7 +10455,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10468,13 +10476,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10482,10 +10490,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10508,19 +10516,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10569,7 +10577,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10584,19 +10592,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10604,10 +10612,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10633,16 +10641,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10691,7 +10699,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10700,7 +10708,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10709,27 +10717,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10755,16 +10763,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10789,13 +10797,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10813,7 +10821,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10822,7 +10830,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10837,7 +10845,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10848,14 +10856,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10877,16 +10885,16 @@
         <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10911,13 +10919,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10935,7 +10943,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10953,27 +10961,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10996,19 +11004,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11057,7 +11065,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11078,10 +11086,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11092,10 +11100,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11121,13 +11129,13 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11157,7 +11165,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11175,7 +11183,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11193,27 +11201,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11328,10 +11336,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11448,13 +11456,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="B77" t="s" s="2">
-        <v>444</v>
-      </c>
       <c r="C77" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11476,13 +11484,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11568,13 +11576,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>83</v>
@@ -11596,13 +11604,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11688,10 +11696,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11810,10 +11818,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11932,10 +11940,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11961,16 +11969,16 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -11998,10 +12006,10 @@
         <v>326</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12019,7 +12027,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12040,10 +12048,10 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12054,10 +12062,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12080,16 +12088,16 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12139,7 +12147,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12157,27 +12165,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12200,16 +12208,16 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12259,7 +12267,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12277,27 +12285,27 @@
         <v>83</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12320,19 +12328,19 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12381,7 +12389,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12393,7 +12401,7 @@
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
@@ -12402,10 +12410,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12416,10 +12424,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12534,10 +12542,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12654,14 +12662,14 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12683,10 +12691,10 @@
         <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>143</v>
@@ -12741,7 +12749,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12776,10 +12784,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12802,13 +12810,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12859,7 +12867,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12868,7 +12876,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12880,10 +12888,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12894,10 +12902,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12920,13 +12928,13 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12977,7 +12985,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12986,7 +12994,7 @@
         <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -12998,10 +13006,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -13012,10 +13020,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13041,16 +13049,16 @@
         <v>191</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13078,10 +13086,10 @@
         <v>118</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13099,7 +13107,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13117,13 +13125,13 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13134,10 +13142,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13163,16 +13171,16 @@
         <v>191</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13200,10 +13208,10 @@
         <v>326</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13221,7 +13229,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13239,13 +13247,13 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13256,10 +13264,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13282,17 +13290,17 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13341,7 +13349,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13365,7 +13373,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13376,10 +13384,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13405,10 +13413,10 @@
         <v>208</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13459,7 +13467,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13480,10 +13488,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13494,10 +13502,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13520,16 +13528,16 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13579,7 +13587,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13600,10 +13608,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13614,10 +13622,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13640,16 +13648,16 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13699,7 +13707,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13720,10 +13728,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13734,10 +13742,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13760,19 +13768,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13821,7 +13829,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13842,10 +13850,10 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13856,10 +13864,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13974,10 +13982,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14094,14 +14102,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14123,10 +14131,10 @@
         <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>143</v>
@@ -14181,7 +14189,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14216,10 +14224,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14245,13 +14253,13 @@
         <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O100" t="s" s="2">
         <v>325</v>
@@ -14303,7 +14311,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>94</v>
@@ -14321,7 +14329,7 @@
         <v>83</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>331</v>
@@ -14338,10 +14346,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14456,10 +14464,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14576,10 +14584,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14651,7 +14659,7 @@
         <v>83</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
@@ -14696,10 +14704,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14814,10 +14822,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14934,10 +14942,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15056,10 +15064,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15176,10 +15184,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15296,10 +15304,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15416,10 +15424,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15538,13 +15546,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>83</v>
@@ -15569,10 +15577,10 @@
         <v>221</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>224</v>
@@ -15607,7 +15615,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15660,10 +15668,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15778,10 +15786,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15898,10 +15906,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15943,7 +15951,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>83</v>
@@ -16020,10 +16028,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16140,10 +16148,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16260,10 +16268,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16380,10 +16388,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16502,13 +16510,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>83</v>
@@ -16533,10 +16541,10 @@
         <v>221</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>224</v>
@@ -16571,7 +16579,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>83</v>
@@ -16624,10 +16632,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16742,10 +16750,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16862,10 +16870,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16907,7 +16915,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>83</v>
@@ -16984,10 +16992,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17104,10 +17112,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17224,10 +17232,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17344,10 +17352,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17466,10 +17474,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17588,10 +17596,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17614,19 +17622,19 @@
         <v>95</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>83</v>
@@ -17675,7 +17683,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -17693,27 +17701,27 @@
         <v>83</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17739,16 +17747,16 @@
         <v>191</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -17773,13 +17781,13 @@
         <v>83</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>83</v>
@@ -17797,7 +17805,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -17806,7 +17814,7 @@
         <v>94</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>106</v>
@@ -17821,7 +17829,7 @@
         <v>137</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -17832,14 +17840,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17861,16 +17869,16 @@
         <v>191</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -17895,13 +17903,13 @@
         <v>83</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>83</v>
@@ -17919,7 +17927,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -17937,27 +17945,27 @@
         <v>83</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17983,16 +17991,16 @@
         <v>84</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>83</v>
@@ -18041,7 +18049,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18062,10 +18070,10 @@
         <v>83</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="611">
   <si>
     <t>Property</t>
   </si>
@@ -658,6 +658,14 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="exam"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -812,9 +820,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>exam</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -952,9 +957,6 @@
     <t>Observation.category:second.coding.code</t>
   </si>
   <si>
-    <t>LP89803-8</t>
-  </si>
-  <si>
     <t>Observation.category:second.coding.display</t>
   </si>
   <si>
@@ -973,6 +975,14 @@
     <t>このObservationに関する詳細分類、JP_ObservationDetailedDentalCategory_VSより選択する、必須項目</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS"/&gt;
+    &lt;code value="DO-1-03"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDetailedDentalCategory_VS</t>
   </si>
   <si>
@@ -994,16 +1004,10 @@
     <t>Observation.category:third.coding.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS</t>
-  </si>
-  <si>
     <t>Observation.category:third.coding.version</t>
   </si>
   <si>
     <t>Observation.category:third.coding.code</t>
-  </si>
-  <si>
-    <t>DO-1-03</t>
   </si>
   <si>
     <t>Observation.category:third.coding.display</t>
@@ -1114,7 +1118,7 @@
     <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
+    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
@@ -1159,7 +1163,7 @@
 </t>
   </si>
   <si>
-    <t>このobservationが行われるヘルスケアイベント</t>
+    <t>このobservationが行われる診療イベント</t>
   </si>
   <si>
     <t>例：診療、歯科検診、身元不明者調査</t>
@@ -4148,7 +4152,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -4167,7 +4171,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4220,10 +4224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4246,13 +4250,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4303,7 +4307,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4327,7 +4331,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4338,10 +4342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4370,7 +4374,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4411,10 +4415,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4423,7 +4427,7 @@
         <v>198</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4447,7 +4451,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4458,10 +4462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4484,19 +4488,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4545,7 +4549,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4566,10 +4570,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4580,10 +4584,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4606,13 +4610,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4663,7 +4667,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4687,7 +4691,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4698,10 +4702,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4730,7 +4734,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4771,10 +4775,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -4783,7 +4787,7 @@
         <v>198</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4807,7 +4811,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4818,10 +4822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4847,23 +4851,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4905,7 +4909,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4926,10 +4930,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4940,10 +4944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4966,16 +4970,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5025,7 +5029,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5046,10 +5050,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5060,10 +5064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5089,21 +5093,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>256</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -5206,7 +5210,7 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>262</v>
@@ -5448,7 +5452,7 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>280</v>
@@ -5671,7 +5675,7 @@
         <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5694,13 +5698,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5751,7 +5755,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5775,7 +5779,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5789,7 +5793,7 @@
         <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5818,7 +5822,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5859,10 +5863,10 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
@@ -5871,7 +5875,7 @@
         <v>198</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5895,7 +5899,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5909,7 +5913,7 @@
         <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5932,19 +5936,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5993,7 +5997,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6014,10 +6018,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -6031,7 +6035,7 @@
         <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6054,13 +6058,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6111,7 +6115,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6135,7 +6139,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6149,7 +6153,7 @@
         <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6178,7 +6182,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6219,10 +6223,10 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
@@ -6231,7 +6235,7 @@
         <v>198</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6255,7 +6259,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6269,7 +6273,7 @@
         <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6295,16 +6299,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6353,7 +6357,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6374,10 +6378,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6391,7 +6395,7 @@
         <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6414,16 +6418,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6473,7 +6477,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6494,10 +6498,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6511,7 +6515,7 @@
         <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6537,21 +6541,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6628,7 +6632,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>261</v>
@@ -6654,7 +6658,7 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>262</v>
@@ -6748,7 +6752,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>269</v>
@@ -6870,7 +6874,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>279</v>
@@ -6896,7 +6900,7 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>280</v>
@@ -6992,13 +6996,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>189</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -7023,10 +7027,10 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>290</v>
@@ -7042,7 +7046,7 @@
         <v>83</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>83</v>
@@ -7117,7 +7121,7 @@
         <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7140,13 +7144,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7197,7 +7201,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7221,7 +7225,7 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7235,7 +7239,7 @@
         <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7264,7 +7268,7 @@
         <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>143</v>
@@ -7305,10 +7309,10 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
@@ -7317,7 +7321,7 @@
         <v>198</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7341,7 +7345,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7355,7 +7359,7 @@
         <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7378,19 +7382,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7439,7 +7443,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7460,10 +7464,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7477,7 +7481,7 @@
         <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7500,13 +7504,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7557,7 +7561,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7581,7 +7585,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7595,7 +7599,7 @@
         <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7624,7 +7628,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7665,10 +7669,10 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
@@ -7677,7 +7681,7 @@
         <v>198</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7701,7 +7705,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7715,7 +7719,7 @@
         <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7741,23 +7745,23 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7799,7 +7803,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7820,10 +7824,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7834,10 +7838,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7860,16 +7864,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7919,7 +7923,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7940,10 +7944,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7954,10 +7958,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7983,21 +7987,21 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -8074,7 +8078,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>261</v>
@@ -8100,7 +8104,7 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>262</v>
@@ -8194,7 +8198,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>269</v>
@@ -8316,7 +8320,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>279</v>
@@ -8342,7 +8346,7 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>280</v>
@@ -8438,14 +8442,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8467,16 +8471,16 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8501,14 +8505,14 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8525,7 +8529,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8540,30 +8544,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8586,13 +8590,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8643,7 +8647,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8667,7 +8671,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8678,10 +8682,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8710,7 +8714,7 @@
         <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8751,10 +8755,10 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
@@ -8763,7 +8767,7 @@
         <v>198</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8787,7 +8791,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8798,10 +8802,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8824,19 +8828,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8885,7 +8889,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8906,10 +8910,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8920,10 +8924,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8946,13 +8950,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9003,7 +9007,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9027,7 +9031,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -9038,10 +9042,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9070,7 +9074,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -9111,10 +9115,10 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>83</v>
@@ -9123,7 +9127,7 @@
         <v>198</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9147,7 +9151,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9158,10 +9162,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9187,23 +9191,23 @@
         <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9245,7 +9249,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9266,10 +9270,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9280,10 +9284,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9306,16 +9310,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9365,7 +9369,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9386,10 +9390,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9400,10 +9404,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9429,21 +9433,21 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9520,10 +9524,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9546,7 +9550,7 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>262</v>
@@ -9566,7 +9570,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9640,10 +9644,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9762,10 +9766,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9788,7 +9792,7 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>280</v>
@@ -9884,10 +9888,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9910,19 +9914,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9971,7 +9975,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9986,19 +9990,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AL64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10006,10 +10010,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10032,16 +10036,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10091,7 +10095,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10112,13 +10116,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10126,14 +10130,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10152,19 +10156,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10213,7 +10217,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10228,19 +10232,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10248,14 +10252,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10274,19 +10278,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10335,7 +10339,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10350,19 +10354,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10370,10 +10374,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10396,16 +10400,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10455,7 +10459,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10476,13 +10480,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10490,10 +10494,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10516,19 +10520,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10577,7 +10581,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10592,19 +10596,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10612,10 +10616,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10641,16 +10645,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O70" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10699,7 +10703,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10708,7 +10712,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10717,27 +10721,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10763,16 +10767,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O71" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10797,40 +10801,40 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Y71" t="s" s="2">
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI71" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10845,7 +10849,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10856,14 +10860,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10885,16 +10889,16 @@
         <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O72" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10919,13 +10923,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10943,7 +10947,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10961,27 +10965,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>428</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11004,19 +11008,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11065,7 +11069,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11086,10 +11090,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11100,10 +11104,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11129,13 +11133,13 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11165,7 +11169,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11183,7 +11187,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11201,27 +11205,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>443</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11244,13 +11248,13 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11301,7 +11305,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11325,7 +11329,7 @@
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11336,10 +11340,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11368,7 +11372,7 @@
         <v>141</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>143</v>
@@ -11409,10 +11413,10 @@
         <v>83</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>83</v>
@@ -11421,7 +11425,7 @@
         <v>198</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11445,7 +11449,7 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11456,13 +11460,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B77" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11484,13 +11488,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11541,7 +11545,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11576,13 +11580,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>83</v>
@@ -11604,13 +11608,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11661,7 +11665,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11696,10 +11700,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11722,19 +11726,19 @@
         <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11783,7 +11787,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11804,10 +11808,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11818,10 +11822,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11844,7 +11848,7 @@
         <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>280</v>
@@ -11940,10 +11944,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11969,16 +11973,16 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O81" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12003,13 +12007,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12027,7 +12031,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12048,10 +12052,10 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12062,10 +12066,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12088,16 +12092,16 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12147,7 +12151,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12165,27 +12169,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AO82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>471</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12208,16 +12212,16 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12267,7 +12271,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12285,27 +12289,27 @@
         <v>83</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>479</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12328,19 +12332,19 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12389,7 +12393,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12401,19 +12405,19 @@
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12424,10 +12428,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12450,13 +12454,13 @@
         <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12507,7 +12511,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12531,7 +12535,7 @@
         <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12542,10 +12546,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12574,7 +12578,7 @@
         <v>141</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>143</v>
@@ -12627,7 +12631,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12651,7 +12655,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12662,14 +12666,14 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12691,10 +12695,10 @@
         <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>143</v>
@@ -12749,7 +12753,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12784,10 +12788,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12810,13 +12814,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12867,7 +12871,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12876,7 +12880,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12888,10 +12892,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12902,10 +12906,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12928,13 +12932,13 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12985,7 +12989,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12994,7 +12998,7 @@
         <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -13006,10 +13010,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -13020,10 +13024,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13049,16 +13053,16 @@
         <v>191</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13086,10 +13090,10 @@
         <v>118</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13107,7 +13111,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13125,13 +13129,13 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13142,10 +13146,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13171,16 +13175,16 @@
         <v>191</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13205,13 +13209,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13229,7 +13233,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13247,13 +13251,13 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13264,10 +13268,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13290,17 +13294,17 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13349,7 +13353,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13373,7 +13377,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13384,10 +13388,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13410,13 +13414,13 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13467,7 +13471,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13488,10 +13492,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13502,10 +13506,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13528,16 +13532,16 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13587,7 +13591,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13608,10 +13612,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13622,10 +13626,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13648,16 +13652,16 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13707,7 +13711,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13728,10 +13732,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13742,10 +13746,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13768,19 +13772,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="O96" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13829,7 +13833,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13850,10 +13854,10 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13864,10 +13868,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13890,13 +13894,13 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13947,7 +13951,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13971,7 +13975,7 @@
         <v>83</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13982,10 +13986,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14014,7 +14018,7 @@
         <v>141</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>143</v>
@@ -14067,7 +14071,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14091,7 +14095,7 @@
         <v>83</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14102,14 +14106,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14131,10 +14135,10 @@
         <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>143</v>
@@ -14189,7 +14193,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14224,10 +14228,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14253,16 +14257,16 @@
         <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M100" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>555</v>
-      </c>
       <c r="O100" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -14287,14 +14291,14 @@
         <v>83</v>
       </c>
       <c r="X100" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z100" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Y100" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
       </c>
@@ -14311,7 +14315,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>94</v>
@@ -14329,16 +14333,16 @@
         <v>83</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AM100" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AO100" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
@@ -14346,10 +14350,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14372,13 +14376,13 @@
         <v>83</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14429,7 +14433,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14453,7 +14457,7 @@
         <v>83</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14464,10 +14468,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14496,7 +14500,7 @@
         <v>141</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>143</v>
@@ -14537,10 +14541,10 @@
         <v>83</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>83</v>
@@ -14549,7 +14553,7 @@
         <v>198</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14573,7 +14577,7 @@
         <v>83</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14584,10 +14588,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14610,19 +14614,19 @@
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -14659,7 +14663,7 @@
         <v>83</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
@@ -14669,7 +14673,7 @@
         <v>198</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14690,10 +14694,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14704,10 +14708,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14730,13 +14734,13 @@
         <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14787,7 +14791,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14811,7 +14815,7 @@
         <v>83</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14822,10 +14826,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14854,7 +14858,7 @@
         <v>141</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>143</v>
@@ -14895,10 +14899,10 @@
         <v>83</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>83</v>
@@ -14907,7 +14911,7 @@
         <v>198</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14931,7 +14935,7 @@
         <v>83</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14942,10 +14946,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14971,16 +14975,16 @@
         <v>108</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15029,7 +15033,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15050,10 +15054,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15064,10 +15068,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15090,16 +15094,16 @@
         <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15149,7 +15153,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15170,10 +15174,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15184,10 +15188,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15213,14 +15217,14 @@
         <v>114</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -15304,10 +15308,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15330,7 +15334,7 @@
         <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>262</v>
@@ -15424,10 +15428,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15546,13 +15550,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>83</v>
@@ -15574,19 +15578,19 @@
         <v>95</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15615,7 +15619,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15633,7 +15637,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -15654,10 +15658,10 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
@@ -15668,10 +15672,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15694,13 +15698,13 @@
         <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15751,7 +15755,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15775,7 +15779,7 @@
         <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
@@ -15786,10 +15790,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15818,7 +15822,7 @@
         <v>141</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>143</v>
@@ -15859,10 +15863,10 @@
         <v>83</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>83</v>
@@ -15871,7 +15875,7 @@
         <v>198</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15895,7 +15899,7 @@
         <v>83</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
@@ -15906,10 +15910,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15935,23 +15939,23 @@
         <v>108</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>83</v>
@@ -15993,7 +15997,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16014,10 +16018,10 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>83</v>
@@ -16028,10 +16032,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16054,16 +16058,16 @@
         <v>95</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16113,7 +16117,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16134,10 +16138,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
@@ -16148,10 +16152,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16177,14 +16181,14 @@
         <v>114</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -16268,10 +16272,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16294,7 +16298,7 @@
         <v>95</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L117" t="s" s="2">
         <v>262</v>
@@ -16388,10 +16392,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16510,13 +16514,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>83</v>
@@ -16538,19 +16542,19 @@
         <v>95</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>83</v>
@@ -16579,7 +16583,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>83</v>
@@ -16597,7 +16601,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16618,10 +16622,10 @@
         <v>83</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>83</v>
@@ -16632,10 +16636,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16658,13 +16662,13 @@
         <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16715,7 +16719,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -16739,7 +16743,7 @@
         <v>83</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>83</v>
@@ -16750,10 +16754,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16782,7 +16786,7 @@
         <v>141</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>143</v>
@@ -16823,10 +16827,10 @@
         <v>83</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>83</v>
@@ -16835,7 +16839,7 @@
         <v>198</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -16859,7 +16863,7 @@
         <v>83</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>83</v>
@@ -16870,10 +16874,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16899,23 +16903,23 @@
         <v>108</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>83</v>
@@ -16957,7 +16961,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -16978,10 +16982,10 @@
         <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>83</v>
@@ -16992,10 +16996,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17018,16 +17022,16 @@
         <v>95</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17077,7 +17081,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17098,10 +17102,10 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>83</v>
@@ -17112,10 +17116,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17141,14 +17145,14 @@
         <v>114</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -17232,10 +17236,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17258,7 +17262,7 @@
         <v>95</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>262</v>
@@ -17352,10 +17356,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17474,10 +17478,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17500,7 +17504,7 @@
         <v>95</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L127" t="s" s="2">
         <v>280</v>
@@ -17596,10 +17600,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17622,19 +17626,19 @@
         <v>95</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="L128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M128" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>597</v>
-      </c>
       <c r="O128" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>83</v>
@@ -17683,7 +17687,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -17701,27 +17705,27 @@
         <v>83</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AM128" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP128" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP128" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17747,16 +17751,16 @@
         <v>191</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="N129" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="M129" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>602</v>
-      </c>
       <c r="O129" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -17781,40 +17785,40 @@
         <v>83</v>
       </c>
       <c r="X129" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z129" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Y129" t="s" s="2">
+      <c r="AA129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI129" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>106</v>
@@ -17829,7 +17833,7 @@
         <v>137</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -17840,14 +17844,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17869,16 +17873,16 @@
         <v>191</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N130" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -17903,13 +17907,13 @@
         <v>83</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>83</v>
@@ -17927,7 +17931,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -17945,27 +17949,27 @@
         <v>83</v>
       </c>
       <c r="AL130" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN130" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AM130" t="s" s="2">
+      <c r="AO130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP130" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP130" t="s" s="2">
-        <v>428</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17991,16 +17995,16 @@
         <v>84</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>83</v>
@@ -18049,7 +18053,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18070,10 +18074,10 @@
         <v>83</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>83</v>
